--- a/assignment3/data/trainingdataset_ontario_budgets_v21_llm_sample.xlsx
+++ b/assignment3/data/trainingdataset_ontario_budgets_v21_llm_sample.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{896E3E48-27F7-1F49-B3F2-3CAB47B0D443}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5100" yWindow="1140" windowWidth="30160" windowHeight="19660" xr2:uid="{FB597964-1960-7349-B80F-395C3D8D9DDC}"/>
+    <workbookView xWindow="5080" yWindow="1140" windowWidth="30160" windowHeight="19660" xr2:uid="{FB597964-1960-7349-B80F-395C3D8D9DDC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
